--- a/ksoft/docs/records/Supplier_Group_Records.xlsx
+++ b/ksoft/docs/records/Supplier_Group_Records.xlsx
@@ -1480,13 +1480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAF38D8-46D5-49C1-9AD0-3ED61A0E9EB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B033329-D490-4514-9BCE-029C3F630F11}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B181673-DE60-4AFA-B7CE-C773C0B56BAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE6E1B2E-DF2E-4F26-B578-FFBB5871214E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C984DB8-0571-45CC-B57C-6190E163B9BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6494E00D-4827-40F0-B3DE-84692AA59C06}"/>
 </file>
--- a/ksoft/docs/records/Supplier_Group_Records.xlsx
+++ b/ksoft/docs/records/Supplier_Group_Records.xlsx
@@ -1480,13 +1480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B033329-D490-4514-9BCE-029C3F630F11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAF38D8-46D5-49C1-9AD0-3ED61A0E9EB8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE6E1B2E-DF2E-4F26-B578-FFBB5871214E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B181673-DE60-4AFA-B7CE-C773C0B56BAA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6494E00D-4827-40F0-B3DE-84692AA59C06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C984DB8-0571-45CC-B57C-6190E163B9BD}"/>
 </file>